--- a/artfynd/A 30854-2024 artfynd.xlsx
+++ b/artfynd/A 30854-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7118223</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R2" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2014-01-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-01-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53529928</v>
+        <v>53529863</v>
       </c>
       <c r="B3" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +785,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102995</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,14 +804,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R3" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -912,32 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53529923</v>
+        <v>65834029</v>
       </c>
       <c r="B4" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102952</v>
+        <v>100044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Kornknarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Crex crex</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,14 +922,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R4" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,22 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2017-05-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mellan Edared -Vilg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,32 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>53530022</v>
+        <v>62709530</v>
       </c>
       <c r="B5" t="n">
-        <v>56608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102981</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,14 +1045,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1086,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R5" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2017-01-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2017-01-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,39 +1126,34 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lennart Walldén, Gunnel Wallden</t>
+          <t>Lennart Walldén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53529863</v>
+        <v>61683116</v>
       </c>
       <c r="B6" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>100082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R6" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,7 +1209,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1249,12 +1219,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2016-10-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,61 +1251,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53529974</v>
+        <v>59998843</v>
       </c>
       <c r="B7" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edared, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R7" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,22 +1329,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59998843</v>
+        <v>59821885</v>
       </c>
       <c r="B8" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>102118</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1442,25 +1404,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edared, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R8" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,7 +1447,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2016-05-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1497,12 +1457,17 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2016-05-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>00:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På vägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,22 +1487,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lennart Walldén, Gunnel Wallden</t>
+          <t>Lennart Walldén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59998833</v>
+        <v>66118049</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,47 +1505,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>102626</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edared, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R9" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1612,22 +1570,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2017-06-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>N Väst om</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,37 +1617,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60177843</v>
+        <v>53529923</v>
       </c>
       <c r="B10" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>102952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1692,25 +1650,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edared, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R10" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1737,22 +1693,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-06-17</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-06-17</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,44 +1728,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lennart Walldén</t>
+          <t>Lennart Walldén, Gunnel Wallden</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62674739</v>
+        <v>53529974</v>
       </c>
       <c r="B11" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103035</v>
+        <v>102976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1821,7 +1772,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1830,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R11" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1860,22 +1811,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-01-02</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-01-02</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,22 +1846,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lennart Walldén</t>
+          <t>Lennart Walldén, Gunnel Wallden</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65834029</v>
+        <v>53530030</v>
       </c>
       <c r="B12" t="n">
-        <v>55729</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,33 +1864,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100044</v>
+        <v>102980</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknarr</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crex crex</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1953,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>347146.5209202949</v>
+        <v>347147</v>
       </c>
       <c r="R12" t="n">
-        <v>6373371.155223071</v>
+        <v>6373371</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1983,27 +1929,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2017-05-25</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mellan Edared -Vilg</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,6 +1968,600 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>53530022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58212</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102981</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Edared, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>347147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6373371</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fotskäl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-05-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-05-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lennart Walldén, Gunnel Wallden</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>53529928</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Edared, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>347147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6373371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fotskäl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-05-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-05-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lennart Walldén, Gunnel Wallden</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>62674739</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Edared, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>347147</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6373371</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fotskäl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-01-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-01-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>59998833</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Edared, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>347147</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6373371</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fotskäl</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-06-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-06-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lennart Walldén, Gunnel Wallden</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>60177843</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Edared, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>347147</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6373371</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fotskäl</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2016-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2016-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lennart Walldén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
